--- a/src/attributions/attributions_ig_traj_460.xlsx
+++ b/src/attributions/attributions_ig_traj_460.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,49 +1002,49 @@
         <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1196116061141161</v>
+        <v>0.1196012875771676</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.290569133234185</v>
+        <v>0.07149368836148631</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006638047860872211</v>
+        <v>-0.1337936141904411</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.08015518083814908</v>
+        <v>0.1204644326784856</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2541322985548342</v>
+        <v>-0.1573973487027684</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02476157060175758</v>
+        <v>-0.1117632887167325</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
@@ -1056,106 +1056,106 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1114215457575703</v>
+        <v>-0.01718967796414121</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01317060550227939</v>
+        <v>-0.1382571262468925</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.01740300039027242</v>
+        <v>0.06796678067283465</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.007358126984907245</v>
+        <v>0.002687506606926044</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0209489242586958</v>
+        <v>0.08312824381990981</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.001278400681974891</v>
+        <v>0.004603062189039444</v>
       </c>
       <c r="AG2" t="n">
         <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.05293777923492834</v>
+        <v>0.1006100504657773</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.04805918661798327</v>
+        <v>-0.09756110034889687</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07416228179326181</v>
+        <v>0.2231328508953532</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1561542071371479</v>
+        <v>0.3829220191024981</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1159826283168068</v>
+        <v>-0.1108405766309989</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.02550510037105823</v>
+        <v>0.0888817369892551</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
@@ -1164,79 +1164,79 @@
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01975330946610538</v>
+        <v>-0.08816923832859555</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1173026497105192</v>
+        <v>0.07658463836807043</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.01848489159634745</v>
+        <v>-0.08448447230201303</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01234147895666798</v>
+        <v>0.009611671176379673</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04048451837496309</v>
+        <v>-0.005555317869351742</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.04534039424958565</v>
+        <v>0.01478125945156264</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.05915712025865116</v>
+        <v>0.1193240257685157</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02790266473584342</v>
+        <v>-0.1963734529935547</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.0324154409580402</v>
+        <v>0.003211026096227493</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1245,52 +1245,52 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.02752952368981012</v>
+        <v>-0.147578627845049</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.04935487713575477</v>
+        <v>-0.0384580008902099</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01352769766097447</v>
+        <v>-0.001058525450520398</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.02357779391119231</v>
+        <v>-0.1218212521010368</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.01519330751800707</v>
+        <v>0.1565628203488918</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.0674696792572889</v>
+        <v>0.009909154309077069</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
@@ -1299,19 +1299,19 @@
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04430740944458727</v>
+        <v>-0.1559629877789417</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04969995472952137</v>
+        <v>-0.02609993524219233</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.004314839788907577</v>
+        <v>0.03603319553740546</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1323,28 +1323,28 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.04071710234245642</v>
+        <v>-0.06247178305906249</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.006051752272508887</v>
+        <v>0.101043293208645</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05840709464602017</v>
+        <v>-0.02589586382847748</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.02989034350703162</v>
+        <v>-0.008934436063139083</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04157758598046472</v>
+        <v>-0.03564070463994178</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.06208716646384525</v>
+        <v>-0.03186828665772968</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,22 +1377,22 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.05999670130279144</v>
+        <v>-0.03097103455510533</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.005262735983777017</v>
+        <v>0.1172190546843655</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03917335870846283</v>
+        <v>0.2420069552513112</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1407,19 +1407,19 @@
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04390391319024155</v>
+        <v>-0.1653635536830066</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.09826642592587737</v>
+        <v>0.1447208937899271</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01862336688472342</v>
+        <v>0.06734954620934963</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
@@ -1428,28 +1428,28 @@
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.05288800328953746</v>
+        <v>-0.04154932617205117</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.05981517127729411</v>
+        <v>0.005406520769501569</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0196735427834946</v>
+        <v>0.05984113922053956</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.0387038909027299</v>
+        <v>-0.209680330044125</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.04123072011519976</v>
+        <v>0.008456027182760657</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01666623914432457</v>
+        <v>0.03023021023969801</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
@@ -1488,76 +1488,76 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.009345571191879251</v>
+        <v>-0.2152877853140302</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.01487059634927098</v>
+        <v>0.02434279710291211</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.02129248369880309</v>
+        <v>0.1142597823783201</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.002131586852149674</v>
+        <v>-0.05570412078670654</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.009157938490005671</v>
+        <v>0.2182106210935311</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.002676297973793981</v>
+        <v>-0.06197480896796694</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.0440100622146601</v>
+        <v>-0.01986568884937685</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.01701625603450851</v>
+        <v>-0.05176899402419473</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,106 +1568,106 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.005440582898757791</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.0003495196798416936</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.004653952028728388</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.004779335034567648</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.002297010291088133</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.0001293584796551266</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.01079681583255226</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.004566624060925512</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.007450962861510229</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.000181379877905519</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>0.001262855375318204</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.002951326977611862</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.01213408105134632</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1685,70 +1685,70 @@
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.008809294310247285</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.006828440715407823</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.01674432099948971</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.03436208348766952</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.007608755845302518</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.009593683336985844</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.009835482895878579</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.001216118430847028</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,25 +1757,25 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.006131333986073032</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.00712081922806476</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-2.461088886427914e-12</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1784,25 +1784,25 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.0138765649282214</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.0008701596137953882</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.009631107679849781</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
@@ -1811,34 +1811,34 @@
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0.0001154767215185917</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.001617826998928952</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.002842370399107497</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.003685210598822428</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,97 +1847,97 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.02374283606794928</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.008253312195646619</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.003200157294702438</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.00529361368586902</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.004137014881393988</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.001985119589781192</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.01306546327202614</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.00307190082752162</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.01124936056504306</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.02178639191246748</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.008307887771974616</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,52 +1946,52 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.003712722057874629</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>-0.004150674059873234</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.0110458445136107</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.008153975715620482</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.003619578626316912</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0.003039995938310578</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,25 +2000,25 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0.0006150511971471157</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.007695692405970492</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.004494640550891518</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2027,64 +2027,64 @@
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.003478681352035726</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.008249662569360735</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.006750996823763457</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0.004719922193098929</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.01978609095705192</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.005186197345335941</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0.02655440159698456</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,28 +2093,28 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.0003226231426340808</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.0001453817809119211</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.003566062591383966</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
@@ -2123,15 +2123,8550 @@
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01870761469874</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.3617851184099269</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07315649305868484</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1288687299558038</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.3414444435685571</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1138717397691318</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02804192424334469</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.09914896063732795</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.04209979261661543</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.08620524526150244</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.01310193944797138</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.007764336786340371</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.01181192408789911</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.2717562727110402</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.2473645309424141</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.1073850498703486</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.5487936920955847</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.1345657104040734</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.1731488990339077</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.02113314206318945</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.01202982874695622</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.001083575727403763</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.05734753178232829</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.02921540561188522</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.006940450764099293</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.4526917301177376</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.03643016342323827</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.1907115960556312</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.3240809579637304</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.01639028902041008</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-0.1025951354114756</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.2907111002870302</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.02111543549543464</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.1428435709370913</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.3198840489552468</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.02607217999664791</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>-0.1073656269844935</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.08718919331317114</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.01468291189574659</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-0.09117171758387528</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.165430139297159</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.01279074510601251</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.02650811029358422</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>-0.1376106589738356</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.01491362884179283</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.2419471457836141</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.2233083246320357</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.01030917391740928</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-0.03653336247471291</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.2008065047831364</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.05522208599731845</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>-0.01769410448508891</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.3436831325082361</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.01160984932871688</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>-0.102252914115837</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.1340951741830436</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.0720791246302139</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>-0.07294413591211205</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.3306735775429457</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.02790255171261118</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>-0.1510877532517576</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.2092667871119216</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>-0.03770832037184304</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.001928172484010978</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03602311301892612</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.01520382897529418</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.008679098443695828</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05155282018994375</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.01533556360509918</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.02346641875959721</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.0143043530000325</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.009065709074459239</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.0006731722821654737</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.00162136054466824</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0003160116314612312</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.0217202365290677</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.02316733576801388</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.001015127757843876</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.03088356722403148</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.04798546186398083</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.006923429331409863</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.03138401123550466</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.002727769236873534</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.004935464630408971</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.007415846549853629</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.00563665230385741</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.009628898254834921</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.02204163899159698</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.02392558703801681</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.01374818674637476</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.001853214800165429</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.01597763458380562</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.01686370443854157</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.01085338141993848</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.02300100147361096</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.02587525710012915</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.002124753341531262</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.01872214612917145</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.01733058100439655</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.002690078772725313</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.00032035100416812</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.005564885832083487</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.01028236985327687</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.02698186114359967</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.003414653766485685</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.01234816113939458</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.02446530733550262</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>-0.02140528392537294</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.0112771202340804</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.01864162857048215</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.005896730466479672</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0.01718805512008834</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>-0.02418519371264804</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0.009986983254905846</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0.0004702520361440824</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>-0.01522313100574135</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.01966087279578612</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0.0159547567941267</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0.006507244149731165</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0.02142565219011599</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0.02824437318485554</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>-0.06813813259693625</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0.00666400176953203</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>-0.02555335294312802</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0.01148776549133432</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.02631832050027777</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01619020834467378</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.0320234333113566</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.04263114876287396</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.009360279899686449</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.009899494143486868</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.01715816066772771</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.04011450270644754</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.01186416468374542</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.0201704789109968</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.01074135712032974</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.01017442096614123</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.060194918680078</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.03473782322951706</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.008758750566946194</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.1451363675485339</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.1237903233569984</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.07407851753369346</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.004547151092211679</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.0802165863928975</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.04315908501254177</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.01625266061058005</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.03923038323065468</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.06731013438895576</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.08239950488245994</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.1152768834255896</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.02342805887429177</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.05777197886436175</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.00842905365959285</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.003335199676261088</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.03118725214050988</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.02777119273747287</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.06393891640686461</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.04444816822067579</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.004879400975899504</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.01558724710924005</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.0214153159552811</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.02142965333456042</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.001247749529381394</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.004087995300383129</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0.02877630598208611</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.07322915093734367</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.06397110728312153</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.06418821365728641</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.0260977497943167</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.01132820725956386</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.02442373112372163</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.01487182147025633</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.01531249882937978</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.03000994244593154</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.02719279878258032</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.0450914750902932</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>-0.00819837192178478</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.005024755969528443</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.03655677126773767</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0.02210027284827051</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0.07995227337622481</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.0005913805922526213</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.002431938859570237</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.0812910106868726</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.0303906869074291</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0.03660908705424672</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2438140104374796</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.05897947482454025</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.09895797474459693</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.3717847592794043</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.09934160676706064</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.08317198342287468</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.09854528103425583</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.04365805019363878</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.04712206337489661</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.0345410292889374</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.06805454446039355</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.03284627789172018</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.03935449997160004</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.112618544810269</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.0472293185502284</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.5768390467908372</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.1848321944993935</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.1428085033173116</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.09547589209767043</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.05962865836471717</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.008984434010459223</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.09667115382449706</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.103040114763131</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.06915467523101758</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.3575703829052105</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.03388085462165646</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.01466520817786422</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.09859882158881642</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.04951371960323123</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.03911221667092606</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0.2175476462162297</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.1226747657755736</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0.08491048689024994</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.08971796303069844</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.02056922816495237</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.05177005588135786</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.1104355102572353</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0.078753784644568</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-0.003097452345968677</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0.01695069231059826</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0.0009606814630977377</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>-0.02955252184369187</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.1033275179588584</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-0.1574439829292733</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>-0.03599450165747608</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.02324280024002687</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0.03325319701169794</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.02249018039022715</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0.009019035417647814</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0.1349737308228415</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.05480760818274671</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0.1195050163343287</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.0230369333010193</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.01590820796751916</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0.1180694088029733</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.0594542120045045</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.03681954658736379</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.009911176940367064</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0.04825863413504058</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>-0.05442309364900996</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>-0.1009742975598097</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.1004920168064101</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2553531050600787</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1148308549473101</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.01971714097764958</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2996712991997637</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1407148565647776</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.02107293414554508</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.07943682016344152</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.03805510958515876</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.05873438455585291</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.03772886292226838</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.04030663765238628</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.03961331350209368</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1185769954064138</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.08064006845006212</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.04231644485075783</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.3061556424352843</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.0789797638510223</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.05564627406396337</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.02582589964511705</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.03395795288682096</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.05039361572091115</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.005763664346824974</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.004560676861987235</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.03627143737238437</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2355087815133165</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.09585496935545322</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.012685937951201</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.1021525321651797</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.07968501790563082</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.001370573906723593</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1303711059023162</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1581449786183667</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.06316726538345402</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.09260029713885162</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.0844619827867832</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.002698065529631183</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.09126875775874871</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.01386581307482652</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.03534802279949138</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.05223461328557003</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.04464301068106658</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.008301145959611149</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0611856660884716</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>-0.04672538190386383</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.02448768425559051</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.06776900164326466</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.04367263046708004</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.02359505354533285</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.02807581308453499</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.02990287984307534</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.02783873560637014</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.1123232901697163</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.08492614215800795</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.004422567794291886</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.06464581007280637</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.06608521933557684</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.02183686356396833</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.001529448260017151</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.02752665350167326</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.02081278085376249</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.1045449595197948</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.01350777454075658</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4101417428224209</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.08714135199804793</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.1295505699742246</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6305063597516433</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.1936214574852103</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.1045598370500909</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1510729532237752</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.08658205761477046</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.04086272322865234</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.03586898384151685</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.2004176408345351</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.07517573427379501</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1184480015191772</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.02297833423437707</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.03011076587914463</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.6700738850025827</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.16466755531418</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.1270726416764614</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.05243339937287918</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.1347001421594399</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.04956975717609277</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.06242478639119051</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.09884427524010782</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.931258563068044e-10</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.4563535464359884</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.03697997451207417</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.01771662465774436</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.173759297196213</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.07063638285587269</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.09810221394063844</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.4502171321988353</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.2070018624885213</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.02280536022151834</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.1697485260334553</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.02749391037012909</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.08575397993938963</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.07911937797169358</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.1616502787795859</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.006030229477625406</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.1303314897241453</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.1076919196836797</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.004525802488017245</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.03587260113632922</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.02632434291744071</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>-0.1976108299183106</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.001639743774756629</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.07518615607744197</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.06777333166762144</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.009791624816237113</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.1318235603195131</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.01230179847534118</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.1950252155912503</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.02019300899689748</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.06510228301553601</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.2404697148534425</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.1878423474281987</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>-0.001520440608753186</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.003485375031596007</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.007865166150707117</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>-0.08566974947101803</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.09333231985922419</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.01409689792300684</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4625985291458899</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.2229314675416205</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.09703556928683144</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5078833474612897</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.2972629041712639</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.1572184299434489</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.127025083255456</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.08063613580279741</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.09792035968598875</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.03904769688692217</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.1300440028780359</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.123224808438905</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2549294852294259</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.1134875473113547</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.1161340963021387</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.618218465290958</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0.1061397018161071</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.1992246445048709</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.1096763231400359</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.05697955290132888</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.1086398533816524</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-0.009585540879183565</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.01871508790133072</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.06607025469601961</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.4422820622298895</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0.1616185980146334</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.07641671505285015</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.1946845483137271</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.1158625080528454</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.03584239175206753</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.2788027095884449</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.2483464702261745</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.1750906092766377</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.1780718345990434</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.1399208434331306</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.03348586685917097</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.1377838503441791</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.03489284068019471</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.07639057916416632</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-0.08234481568237789</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0.05038033027247751</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.03583204363616311</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.1962400095449949</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.06122959574524102</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.1027443986989532</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>-0.120515939380587</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.06921180976428162</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.09047018872893442</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>-0.04571322223922259</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.08504501210139871</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.109308742100079</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>-0.2141252434374782</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.1381089274950866</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.0159026971204016</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0.05718321199258836</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.1070787702964326</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.008112226559795254</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>-2.600729073431942e-05</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.07823037375681928</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.009097659123131634</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0.2098185381896638</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.0575471629231928</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.336555437171674</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.06135777985214551</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3831875123635176</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.5322959566929142</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.01989006624165567</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3735684552517652</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.1510495651428461</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.09037598651087966</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.00505557458641274</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.01453010333144592</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.2225698371873889</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.1727136823176928</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.07418051789501016</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.05946961544428966</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.2018806862531689</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-0.6921133598255487</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.05558959644741981</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.2337612095318796</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.0965666647004194</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.1358275110501495</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.1507899182334823</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.08112366232782088</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.1020209951907418</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-3.718194145957218e-11</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-0.3681874879135075</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.03548164770350216</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.1981712592909533</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.14205265070272</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.02630831910187452</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>-0.1434450051232595</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.3710405097446896</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>-0.2019762968185423</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>-0.1787858820438354</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.1373997448703981</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.005508157843654262</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>-0.1366641806921802</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.04399512734449748</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.1665105289922222</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>-0.02037483112578953</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.00288994479911094</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0.009029970119148658</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.03929529484353187</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.1014483372611934</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>-0.00129252732594246</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.02286279499736099</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.01104739834944932</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.07342795928907851</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>-0.02769800582915644</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.0363411261711775</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.08821937038062756</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.1100062159577582</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.1698255799893039</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.02695968115219097</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>-0.1288260249524605</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.1915178057056446</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.1018649999361152</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.2794059236522565</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.02181785394841021</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.001411196078698003</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.1094384033110605</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.02323524300963118</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>-0.02016941195936797</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.8521741898207786</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7610148214787954</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.1590293003937859</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.030948346621777</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.198092376163393</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.3549557690757274</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1538762780232271</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.07856082154242135</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.04491387327237645</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.06901297423531728</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.4151344332777121</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.08917799026989044</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.3358350434574734</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.06688562957884933</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1843704080767352</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.7515652274408765</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.3111202829117998</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.3791669184269192</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.03425901336022938</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.339070859552255</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.1668456468117795</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.0104489372211212</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.120573772426876</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>5.391258516362525e-10</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.6835525948990074</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0.2477761717805942</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.08926317995012653</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.3027782831610128</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.2907458625873046</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.01215174576711718</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.2866970016915811</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.5290155703216051</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.02313980896112145</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.2799313481649517</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.3221211566982087</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.008817506709471439</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.2008676366526367</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.2674176260221984</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.3326672087908349</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.2669326010670112</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.07376445455335708</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.06355647995906946</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.03264711533961171</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.003889248001339853</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.07962433483931873</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.2174979611892139</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.5394243700642285</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.01627548046626066</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.09697476000370633</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.02036583946922766</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>-0.1550700912562984</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.3567551921458387</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.3726310187149573</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.04068361658316722</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.2313795552786425</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.3692232438707566</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.1532351151485925</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.235211281090005</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.1457506976679876</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.6201771012529933</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.2818869889626164</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.121817566414552</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.4182102635873909</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.07730933570136365</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0271445590950052</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1373598464515578</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.5582559617116557</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1024762648037818</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.03275923703580112</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1658653584695611</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.03854176835004435</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.04402368373643159</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.05310257723196626</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.03036966994973282</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.08626140410628917</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.04648320927851894</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.08110407839814479</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.1679230676679331</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.08697662385629805</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.09492412543531524</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.06044683905310416</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.1003813547803111</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-0.3105594546700547</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.04018886331985888</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.03418749064043157</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.04797008947898689</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.04070295032157441</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.07308687639060855</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.003596734909517082</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.1054279506303625</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.006757273681397562</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0.01771334211930333</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.07019059444594888</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.0207199036913824</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0.1910757328322814</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0.01624811766956018</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.1171720355879913</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.01255757876295064</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.1584651908453561</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0.03572940849079437</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.01156689233554674</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>-0.05262067564262755</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.1794282911614549</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0.03530601052942177</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1652922737872348</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.002340377002484159</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.1677768382696132</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-0.02451585121917291</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.01347198715291073</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0.05865699550850837</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.1084181110425975</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0.02417689948125199</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.2030789274179771</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0.06435784311628988</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.009340300142033863</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0.05629275477521552</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.08930946417871466</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0.09297564020040595</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.05413171524268467</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0.04103022647940748</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.09722130818116703</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.1355096389181554</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.1280525971595849</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.007140694550039794</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0.02201008469554065</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.01590457660435962</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.1709275229195235</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0.01083299609489142</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.03296396236224063</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.0193879382869566</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.1944521642854262</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0.0280155289343028</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.02248600000023977</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>-0.04295573889490944</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>-0.07793827411896206</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0.07432367275257394</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.04503243291798874</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.05316118345111672</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.1260579418641443</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.07061327289728116</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.07637227169882287</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0.002595003511476373</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.1495509502539501</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.08199589018180688</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.007043840645568703</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.4812505909539285</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.1346003350362263</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.4539810334222104</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7175607300572453</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.1203746782026315</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.4176626177243355</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.1288473246025053</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.08960483373768918</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1351555843620722</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.02433782984698394</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.2397522489682087</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.1348512772245947</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.3756813450644333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.01027812760628637</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.2257684267705923</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.6927101401972736</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.2052691809185316</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.01851769448868856</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.3089840788779143</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.2402089304177273</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.5344503416997838</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.03573547479409515</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0.007538291553067738</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.08006297256168936</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.5607559582701246</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0.08449837585039278</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0.009532417136632932</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0.2787166491487047</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.05953199048054728</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.1128318771300184</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0.453757559323839</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.06003513570358562</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.2183160641424161</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0.2464794471965611</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0.06411336693880702</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.07891172023929761</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0.1676010462577616</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0.06201226811917105</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0.06025633625782943</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0.1194743552330198</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>-0.08679863603292676</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0.1282113960953555</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0.39518234609161</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0.0752258880395065</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0.2875787850501768</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0.1039694128390199</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>-0.03176172750316894</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0.03528717220139708</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0.1729177297771897</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>-0.06665709796247939</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0.0101463755286837</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0.2877502852007638</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0.05174198200240752</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.08038156994047339</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0.09310803537476335</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>-0.2470111047322911</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>-0.2215723799648033</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0.001064364902432153</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0.02451212183317173</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0.03457511776364507</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>-0.2395784124678277</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>-0.1111191911000231</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4358881162389499</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.4665358341369724</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.05967315424458394</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8187624612434573</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.7501272762382689</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.02423817662322045</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.195103138700646</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.2206948220417962</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.03496239007907124</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.195864962737386</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.3654710377640693</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.08424208498080478</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.3228706024728611</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.01533692547516372</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.01485166540892556</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.9808531497067868</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.2809957737887471</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.008284703644074255</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.3886786426192624</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.4607811499292275</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.03232934840624061</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.2084005686792265</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.1667104764328936</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0.08817171552524665</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.6937765566182235</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.2819055291605903</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-0.01984065462556177</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.2166194257573555</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.1766007589801243</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0.04204866340646214</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.4884539559219925</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.2954402937282155</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-0.0957619030663415</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-0.1818478995940394</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0.1028967462236994</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0.02047854544230976</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0.004666419966024198</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0.09607982662545272</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>-0.06091255190789997</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0.1629675999192881</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>0.1585230374080115</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0.02880496983189025</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0.3026497077625461</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>-0.209727582339516</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>-0.05737016371054661</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0.04238492667090161</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0.02584807661845962</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0.04186837890151984</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0.05781033287214263</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0.04793486157727723</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>-0.07813421513021714</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0.2357297255283486</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.09139426381853044</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0.04241502533900695</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>-0.01564232026205811</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0.004919815996026486</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0.01468468976300003</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0.003512838620361969</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>0.00574450269229656</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0.0803981901215336</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>-0.07668283123720027</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>-0.05763076706539957</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0.3841911612269514</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.4008540464469843</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2999964386848221</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2819845341839723</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.5347960036257855</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3651388267313203</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.07035307893541624</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.1181248266158188</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1023521540516781</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.1043694511611495</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.06156839807041025</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.1194233913476637</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.03909459294159505</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.1662839526369401</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.01261742698935352</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.01737329036223227</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.4444330835371041</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.1693052025798762</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.2690951360330203</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.03854075793415777</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.1694999746964165</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.004596894777702891</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-0.04469738776790014</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.1244329916737942</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.1000982649237123</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.3637347214052117</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.0953023225613264</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-0.1197832690930122</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.149993582526793</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.07321682521049237</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0.1004187439344823</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.4148206466344767</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.09780553966661852</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-0.0824198103691557</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.151605579276686</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.04632523255661297</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-0.02393289972882566</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.3375234974758008</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>-0.01729599342184493</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>-0.07025269415625678</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0.0110593693575542</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.1125363214117499</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>-0.09533682443345043</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>-0.1167662362972044</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>0.08949980615471874</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0.09450780656572808</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0.09595943874973334</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.04925328960168947</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0.04845219172857585</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.06165847387573953</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>0.1020406116482375</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>-0.1064164978236891</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0.2100836092361924</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0.04574095054302123</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>-0.09469716760519468</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0.1205706414200177</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>-0.1620416164569007</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>-0.001072422972091355</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>-0.00801492386909837</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>-0.01814012379548038</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>-0.06504128608299642</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0.2418965960018615</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG18" t="n">
         <v>0</v>
       </c>
     </row>
